--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,67 +1151,67 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>745</v>
+        <v>645</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4445</v>
+        <v>745</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6490</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>475</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>495</v>
+        <v>475</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1445</v>
+        <v>975</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1221,67 +1221,67 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3750</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3750</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4250</v>
+        <v>490</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4250</v>
+        <v>495</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4750</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4750</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1291,7 +1291,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1301,7 +1301,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1311,170 +1311,270 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>620</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1995</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>925</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1425</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>745</v>
+        <v>620</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1245</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>845</v>
+        <v>690</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>945</v>
+        <v>290</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>975</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>500</v>
+        <v>925</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>500</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>500</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>975</v>
+        <v>845</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3700</v>
+        <v>945</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4450</v>
+        <v>975</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>salnikprivod-l</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>separatornaya-plastina-dq200</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B116" t="n">
         <v>2495</v>
       </c>
     </row>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1381,17 +1381,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>290</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1401,87 +1401,87 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>925</v>
+        <v>290</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1425</v>
+        <v>925</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>745</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1245</v>
+        <v>745</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>845</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>945</v>
+        <v>845</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>975</v>
+        <v>945</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>500</v>
+        <v>975</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -1491,7 +1491,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -1501,7 +1501,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -1511,70 +1511,80 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>245</v>
+        <v>500</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>935</v>
+        <v>245</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2850</v>
+        <v>935</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>975</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3700</v>
+        <v>975</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>4450</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="B117" t="n">
         <v>2495</v>
       </c>
     </row>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +428,11 @@
           <t>avito_site_price</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>фикс (да = цену не пересчитывать)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1331,261 +1337,360 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4250</v>
+        <v>5850</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4750</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>620</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1995</v>
+        <v>620</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>690</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>420</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>290</v>
+        <v>690</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>290</v>
+        <v>420</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>925</v>
+        <v>290</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1425</v>
+        <v>290</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>745</v>
+        <v>925</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1245</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>845</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>945</v>
+        <v>745</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>975</v>
+        <v>745</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>500</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>500</v>
+        <v>845</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>500</v>
+        <v>945</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>500</v>
+        <v>975</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>245</v>
+        <v>500</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>935</v>
+        <v>500</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2850</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>975</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3700</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4450</v>
+        <v>935</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="B121" t="n">
         <v>2495</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Доля от цены маркетплейсов (0.7 = 70%)</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Округление цены, ₽</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Дорогие товары: цена маркетплейса от, ₽</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Доля для дорогих товаров (0.6 = 60%)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3">
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2940</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>940</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="5">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59000</v>
+        <v>70800</v>
       </c>
     </row>
     <row r="6">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4740</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="9">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1740</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="11">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="13">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>995</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>995</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="15">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5990</v>
+        <v>8390</v>
       </c>
     </row>
     <row r="16">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4925</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="17">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39400</v>
+        <v>47280</v>
       </c>
     </row>
     <row r="18">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1740</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="20">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3990</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="21">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3990</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="22">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6445</v>
+        <v>9020</v>
       </c>
     </row>
     <row r="23">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1445</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="24">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="25">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>34400</v>
+        <v>41280</v>
       </c>
     </row>
     <row r="26">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64400</v>
+        <v>77280</v>
       </c>
     </row>
     <row r="27">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="28">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2440</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="29">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="30">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>995</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="31">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1440</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="32">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>745</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="33">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4440</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="34">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4490</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="35">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="36">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="37">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2245</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="38">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>39238</v>
+        <v>47090</v>
       </c>
     </row>
     <row r="39">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2245</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="40">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="41">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="42">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="43">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4440</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="44">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1440</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="45">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4425</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="46">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1440</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="47">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4425</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="48">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>725</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="49">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1240</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="50">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5990</v>
+        <v>8390</v>
       </c>
     </row>
     <row r="51">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>466</v>
+        <v>650</v>
       </c>
     </row>
     <row r="52">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8445</v>
+        <v>11820</v>
       </c>
     </row>
     <row r="53">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>425</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>645</v>
+        <v>900</v>
       </c>
     </row>
     <row r="55">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>745</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="56">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="57">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>745</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="58">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="59">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29450</v>
+        <v>35340</v>
       </c>
     </row>
     <row r="60">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29450</v>
+        <v>35340</v>
       </c>
     </row>
     <row r="61">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29450</v>
+        <v>35340</v>
       </c>
     </row>
     <row r="62">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="63">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>9900</v>
+        <v>13860</v>
       </c>
     </row>
     <row r="64">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1925</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="65">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="66">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4445</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="67">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="68">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2370</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="69">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3345</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="70">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1183</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="71">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="73">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
     </row>
     <row r="74">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>645</v>
+        <v>900</v>
       </c>
     </row>
     <row r="75">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>745</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="76">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4445</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="77">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6490</v>
+        <v>9090</v>
       </c>
     </row>
     <row r="78">
@@ -1201,442 +1201,472 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>475</v>
+        <v>670</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>975</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>495</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1445</v>
+        <v>690</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>245</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>490</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>495</v>
+        <v>690</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3750</v>
+        <v>690</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3750</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4250</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4250</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4750</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4750</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4250</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5850</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>5950</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4250</v>
+        <v>5850</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4750</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>620</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1995</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1995</v>
+        <v>870</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>690</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>420</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>290</v>
+        <v>970</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>290</v>
+        <v>590</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>925</v>
+        <v>410</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1490</v>
+        <v>410</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1425</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>745</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>745</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1245</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>845</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>945</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>975</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>500</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>500</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>500</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>245</v>
+        <v>700</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>935</v>
+        <v>700</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2850</v>
+        <v>700</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>975</v>
+        <v>340</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3700</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4450</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>5180</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>6230</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>2495</v>
+      <c r="B124" t="n">
+        <v>3490</v>
       </c>
     </row>
   </sheetData>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1010</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="49">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2440</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1390</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="14">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3420</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="29">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>690</v>
+        <v>870</v>
       </c>
     </row>
     <row r="36">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1040</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="37">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>690</v>
+        <v>870</v>
       </c>
     </row>
     <row r="43">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2020</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="45">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1740</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="50">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>900</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="55">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1040</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="58">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,6 +431,11 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>фикс (да = цену не пересчитывать)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>site_price (пусто = как Авито)</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1723,6 +1728,48 @@
         <v>0.6</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Режим: «доля» (B1/B4 от цены маркетплейса) или «прибыль» (одинаковая прибыль с Ozon)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>доля</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Налог (УСН доходы), доля</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Комиссия Авито, доля</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Эквайринг сайта, доля</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1256,6 +1256,9 @@
         </is>
       </c>
       <c r="B83" t="n">
+        <v>690</v>
+      </c>
+      <c r="D83" t="n">
         <v>340</v>
       </c>
     </row>
@@ -1266,6 +1269,9 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D84" t="n">
         <v>690</v>
       </c>
     </row>
@@ -1276,6 +1282,9 @@
         </is>
       </c>
       <c r="B85" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D85" t="n">
         <v>690</v>
       </c>
     </row>
@@ -1401,6 +1410,9 @@
         </is>
       </c>
       <c r="B97" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D97" t="n">
         <v>870</v>
       </c>
     </row>
@@ -1571,6 +1583,9 @@
         </is>
       </c>
       <c r="B114" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D114" t="n">
         <v>700</v>
       </c>
     </row>
@@ -1581,6 +1596,9 @@
         </is>
       </c>
       <c r="B115" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D115" t="n">
         <v>700</v>
       </c>
     </row>
@@ -1591,6 +1609,9 @@
         </is>
       </c>
       <c r="B116" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D116" t="n">
         <v>700</v>
       </c>
     </row>
@@ -1601,6 +1622,9 @@
         </is>
       </c>
       <c r="B117" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D117" t="n">
         <v>700</v>
       </c>
     </row>
@@ -1611,6 +1635,9 @@
         </is>
       </c>
       <c r="B118" t="n">
+        <v>690</v>
+      </c>
+      <c r="D118" t="n">
         <v>340</v>
       </c>
     </row>
@@ -1621,6 +1648,9 @@
         </is>
       </c>
       <c r="B119" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D119" t="n">
         <v>1310</v>
       </c>
     </row>
@@ -1641,6 +1671,9 @@
         </is>
       </c>
       <c r="B121" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D121" t="n">
         <v>1370</v>
       </c>
     </row>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -856,6 +856,9 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>4890</v>
+      </c>
+      <c r="D43" t="n">
         <v>6220</v>
       </c>
     </row>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -446,6 +446,9 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>670</v>
+      </c>
+      <c r="D2" t="n">
         <v>620</v>
       </c>
     </row>
@@ -456,6 +459,9 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4090</v>
+      </c>
+      <c r="D3" t="n">
         <v>4120</v>
       </c>
     </row>
@@ -466,6 +472,9 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D4" t="n">
         <v>1320</v>
       </c>
     </row>
@@ -476,6 +485,9 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>71310</v>
+      </c>
+      <c r="D5" t="n">
         <v>70800</v>
       </c>
     </row>
@@ -486,6 +498,9 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D6" t="n">
         <v>2720</v>
       </c>
     </row>
@@ -496,6 +511,9 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>940</v>
+      </c>
+      <c r="D7" t="n">
         <v>1040</v>
       </c>
     </row>
@@ -506,6 +524,9 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>6550</v>
+      </c>
+      <c r="D8" t="n">
         <v>6640</v>
       </c>
     </row>
@@ -516,6 +537,9 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>670</v>
+      </c>
+      <c r="D9" t="n">
         <v>700</v>
       </c>
     </row>
@@ -526,6 +550,9 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>3050</v>
+      </c>
+      <c r="D10" t="n">
         <v>2890</v>
       </c>
     </row>
@@ -536,6 +563,9 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>670</v>
+      </c>
+      <c r="D11" t="n">
         <v>700</v>
       </c>
     </row>
@@ -546,6 +576,9 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>940</v>
+      </c>
+      <c r="D12" t="n">
         <v>1040</v>
       </c>
     </row>
@@ -556,6 +589,9 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D13" t="n">
         <v>1780</v>
       </c>
     </row>
@@ -566,6 +602,9 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D14" t="n">
         <v>1390</v>
       </c>
     </row>
@@ -576,6 +615,9 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>8300</v>
+      </c>
+      <c r="D15" t="n">
         <v>8390</v>
       </c>
     </row>
@@ -596,6 +638,9 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>47310</v>
+      </c>
+      <c r="D17" t="n">
         <v>47280</v>
       </c>
     </row>
@@ -606,6 +651,9 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>2350</v>
+      </c>
+      <c r="D18" t="n">
         <v>2440</v>
       </c>
     </row>
@@ -616,6 +664,9 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D19" t="n">
         <v>2720</v>
       </c>
     </row>
@@ -626,6 +677,9 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D20" t="n">
         <v>5590</v>
       </c>
     </row>
@@ -636,6 +690,9 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D21" t="n">
         <v>5590</v>
       </c>
     </row>
@@ -646,6 +703,9 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D22" t="n">
         <v>9020</v>
       </c>
     </row>
@@ -656,6 +716,9 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D23" t="n">
         <v>2020</v>
       </c>
     </row>
@@ -666,6 +729,9 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D24" t="n">
         <v>2720</v>
       </c>
     </row>
@@ -676,6 +742,9 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>41310</v>
+      </c>
+      <c r="D25" t="n">
         <v>41280</v>
       </c>
     </row>
@@ -686,6 +755,9 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>77310</v>
+      </c>
+      <c r="D26" t="n">
         <v>77280</v>
       </c>
     </row>
@@ -696,6 +768,9 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>670</v>
+      </c>
+      <c r="D27" t="n">
         <v>690</v>
       </c>
     </row>
@@ -706,6 +781,9 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>4450</v>
+      </c>
+      <c r="D28" t="n">
         <v>4240</v>
       </c>
     </row>
@@ -716,6 +794,9 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D29" t="n">
         <v>2720</v>
       </c>
     </row>
@@ -726,6 +807,9 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D30" t="n">
         <v>1390</v>
       </c>
     </row>
@@ -736,6 +820,9 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D31" t="n">
         <v>2020</v>
       </c>
     </row>
@@ -746,6 +833,9 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>940</v>
+      </c>
+      <c r="D32" t="n">
         <v>1040</v>
       </c>
     </row>
@@ -756,6 +846,9 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D33" t="n">
         <v>6220</v>
       </c>
     </row>
@@ -766,6 +859,9 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D34" t="n">
         <v>6290</v>
       </c>
     </row>
@@ -776,6 +872,9 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>940</v>
+      </c>
+      <c r="D35" t="n">
         <v>870</v>
       </c>
     </row>
@@ -786,6 +885,9 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D36" t="n">
         <v>1320</v>
       </c>
     </row>
@@ -796,6 +898,9 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>3050</v>
+      </c>
+      <c r="D37" t="n">
         <v>3140</v>
       </c>
     </row>
@@ -806,6 +911,9 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>47310</v>
+      </c>
+      <c r="D38" t="n">
         <v>47090</v>
       </c>
     </row>
@@ -816,6 +924,9 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>3050</v>
+      </c>
+      <c r="D39" t="n">
         <v>3140</v>
       </c>
     </row>
@@ -826,6 +937,9 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>670</v>
+      </c>
+      <c r="D40" t="n">
         <v>690</v>
       </c>
     </row>
@@ -836,6 +950,9 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>940</v>
+      </c>
+      <c r="D41" t="n">
         <v>1040</v>
       </c>
     </row>
@@ -846,6 +963,9 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>940</v>
+      </c>
+      <c r="D42" t="n">
         <v>870</v>
       </c>
     </row>
@@ -856,7 +976,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4890</v>
+        <v>4800</v>
       </c>
       <c r="D43" t="n">
         <v>6220</v>
@@ -869,6 +989,9 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D44" t="n">
         <v>2530</v>
       </c>
     </row>
@@ -889,6 +1012,9 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D46" t="n">
         <v>2020</v>
       </c>
     </row>
@@ -909,6 +1035,9 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D48" t="n">
         <v>1720</v>
       </c>
     </row>
@@ -919,6 +1048,9 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D49" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -929,6 +1061,9 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>8300</v>
+      </c>
+      <c r="D50" t="n">
         <v>8390</v>
       </c>
     </row>
@@ -939,6 +1074,9 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>670</v>
+      </c>
+      <c r="D51" t="n">
         <v>650</v>
       </c>
     </row>
@@ -949,6 +1087,9 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>11800</v>
+      </c>
+      <c r="D52" t="n">
         <v>11820</v>
       </c>
     </row>
@@ -959,6 +1100,9 @@
         </is>
       </c>
       <c r="B53" t="n">
+        <v>670</v>
+      </c>
+      <c r="D53" t="n">
         <v>600</v>
       </c>
     </row>
@@ -969,6 +1113,9 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D54" t="n">
         <v>1130</v>
       </c>
     </row>
@@ -979,6 +1126,9 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>940</v>
+      </c>
+      <c r="D55" t="n">
         <v>1040</v>
       </c>
     </row>
@@ -989,6 +1139,9 @@
         </is>
       </c>
       <c r="B56" t="n">
+        <v>670</v>
+      </c>
+      <c r="D56" t="n">
         <v>690</v>
       </c>
     </row>
@@ -999,6 +1152,9 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D57" t="n">
         <v>1130</v>
       </c>
     </row>
@@ -1009,6 +1165,9 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>940</v>
+      </c>
+      <c r="D58" t="n">
         <v>1040</v>
       </c>
     </row>
@@ -1019,6 +1178,9 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>35310</v>
+      </c>
+      <c r="D59" t="n">
         <v>35340</v>
       </c>
     </row>
@@ -1029,6 +1191,9 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>35310</v>
+      </c>
+      <c r="D60" t="n">
         <v>35340</v>
       </c>
     </row>
@@ -1039,6 +1204,9 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>35310</v>
+      </c>
+      <c r="D61" t="n">
         <v>35340</v>
       </c>
     </row>
@@ -1049,6 +1217,9 @@
         </is>
       </c>
       <c r="B62" t="n">
+        <v>670</v>
+      </c>
+      <c r="D62" t="n">
         <v>700</v>
       </c>
     </row>
@@ -1059,6 +1230,9 @@
         </is>
       </c>
       <c r="B63" t="n">
+        <v>13900</v>
+      </c>
+      <c r="D63" t="n">
         <v>13860</v>
       </c>
     </row>
@@ -1079,6 +1253,9 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>670</v>
+      </c>
+      <c r="D65" t="n">
         <v>690</v>
       </c>
     </row>
@@ -1089,6 +1266,9 @@
         </is>
       </c>
       <c r="B66" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D66" t="n">
         <v>6220</v>
       </c>
     </row>
@@ -1099,6 +1279,9 @@
         </is>
       </c>
       <c r="B67" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D67" t="n">
         <v>2720</v>
       </c>
     </row>
@@ -1109,6 +1292,9 @@
         </is>
       </c>
       <c r="B68" t="n">
+        <v>3400</v>
+      </c>
+      <c r="D68" t="n">
         <v>3320</v>
       </c>
     </row>
@@ -1119,6 +1305,9 @@
         </is>
       </c>
       <c r="B69" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D69" t="n">
         <v>4680</v>
       </c>
     </row>
@@ -1129,6 +1318,9 @@
         </is>
       </c>
       <c r="B70" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D70" t="n">
         <v>1660</v>
       </c>
     </row>
@@ -1149,6 +1341,9 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>670</v>
+      </c>
+      <c r="D72" t="n">
         <v>690</v>
       </c>
     </row>
@@ -1159,6 +1354,9 @@
         </is>
       </c>
       <c r="B73" t="n">
+        <v>670</v>
+      </c>
+      <c r="D73" t="n">
         <v>690</v>
       </c>
     </row>
@@ -1169,6 +1367,9 @@
         </is>
       </c>
       <c r="B74" t="n">
+        <v>940</v>
+      </c>
+      <c r="D74" t="n">
         <v>900</v>
       </c>
     </row>
@@ -1189,6 +1390,9 @@
         </is>
       </c>
       <c r="B76" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D76" t="n">
         <v>6220</v>
       </c>
     </row>
@@ -1199,6 +1403,9 @@
         </is>
       </c>
       <c r="B77" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D77" t="n">
         <v>9090</v>
       </c>
     </row>
@@ -1219,6 +1426,9 @@
         </is>
       </c>
       <c r="B79" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D79" t="n">
         <v>2720</v>
       </c>
     </row>
@@ -1229,6 +1439,9 @@
         </is>
       </c>
       <c r="B80" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D80" t="n">
         <v>1370</v>
       </c>
     </row>
@@ -1239,6 +1452,9 @@
         </is>
       </c>
       <c r="B81" t="n">
+        <v>670</v>
+      </c>
+      <c r="D81" t="n">
         <v>690</v>
       </c>
     </row>
@@ -1249,6 +1465,9 @@
         </is>
       </c>
       <c r="B82" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D82" t="n">
         <v>2020</v>
       </c>
     </row>
@@ -1259,7 +1478,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="D83" t="n">
         <v>340</v>
@@ -1272,7 +1491,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="D84" t="n">
         <v>690</v>
@@ -1285,7 +1504,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="D85" t="n">
         <v>690</v>
@@ -1298,6 +1517,9 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D86" t="n">
         <v>5250</v>
       </c>
     </row>
@@ -1308,6 +1530,9 @@
         </is>
       </c>
       <c r="B87" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D87" t="n">
         <v>5250</v>
       </c>
     </row>
@@ -1318,6 +1543,9 @@
         </is>
       </c>
       <c r="B88" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D88" t="n">
         <v>5950</v>
       </c>
     </row>
@@ -1328,6 +1556,9 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D89" t="n">
         <v>5950</v>
       </c>
     </row>
@@ -1338,6 +1569,9 @@
         </is>
       </c>
       <c r="B90" t="n">
+        <v>6900</v>
+      </c>
+      <c r="D90" t="n">
         <v>6650</v>
       </c>
     </row>
@@ -1348,6 +1582,9 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>6900</v>
+      </c>
+      <c r="D91" t="n">
         <v>6650</v>
       </c>
     </row>
@@ -1358,6 +1595,9 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D92" t="n">
         <v>5950</v>
       </c>
     </row>
@@ -1383,6 +1623,9 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D94" t="n">
         <v>5950</v>
       </c>
     </row>
@@ -1393,6 +1636,9 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>6900</v>
+      </c>
+      <c r="D95" t="n">
         <v>6650</v>
       </c>
     </row>
@@ -1403,6 +1649,9 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>6900</v>
+      </c>
+      <c r="D96" t="n">
         <v>6650</v>
       </c>
     </row>
@@ -1413,7 +1662,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="D97" t="n">
         <v>870</v>
@@ -1426,6 +1675,9 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D98" t="n">
         <v>2790</v>
       </c>
     </row>
@@ -1436,6 +1688,9 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D99" t="n">
         <v>2790</v>
       </c>
     </row>
@@ -1446,6 +1701,9 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>940</v>
+      </c>
+      <c r="D100" t="n">
         <v>970</v>
       </c>
     </row>
@@ -1456,6 +1714,9 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>670</v>
+      </c>
+      <c r="D101" t="n">
         <v>590</v>
       </c>
     </row>
@@ -1466,6 +1727,9 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>320</v>
+      </c>
+      <c r="D102" t="n">
         <v>410</v>
       </c>
     </row>
@@ -1476,6 +1740,9 @@
         </is>
       </c>
       <c r="B103" t="n">
+        <v>320</v>
+      </c>
+      <c r="D103" t="n">
         <v>410</v>
       </c>
     </row>
@@ -1486,6 +1753,9 @@
         </is>
       </c>
       <c r="B104" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D104" t="n">
         <v>2090</v>
       </c>
     </row>
@@ -1496,6 +1766,9 @@
         </is>
       </c>
       <c r="B105" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D105" t="n">
         <v>2090</v>
       </c>
     </row>
@@ -1526,6 +1799,9 @@
         </is>
       </c>
       <c r="B108" t="n">
+        <v>940</v>
+      </c>
+      <c r="D108" t="n">
         <v>1040</v>
       </c>
     </row>
@@ -1536,6 +1812,9 @@
         </is>
       </c>
       <c r="B109" t="n">
+        <v>940</v>
+      </c>
+      <c r="D109" t="n">
         <v>1040</v>
       </c>
     </row>
@@ -1546,6 +1825,9 @@
         </is>
       </c>
       <c r="B110" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D110" t="n">
         <v>1740</v>
       </c>
     </row>
@@ -1556,6 +1838,9 @@
         </is>
       </c>
       <c r="B111" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D111" t="n">
         <v>1180</v>
       </c>
     </row>
@@ -1566,6 +1851,9 @@
         </is>
       </c>
       <c r="B112" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D112" t="n">
         <v>1320</v>
       </c>
     </row>
@@ -1576,6 +1864,9 @@
         </is>
       </c>
       <c r="B113" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D113" t="n">
         <v>1370</v>
       </c>
     </row>
@@ -1586,7 +1877,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="D114" t="n">
         <v>700</v>
@@ -1599,7 +1890,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="D115" t="n">
         <v>700</v>
@@ -1612,7 +1903,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="D116" t="n">
         <v>700</v>
@@ -1625,7 +1916,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="D117" t="n">
         <v>700</v>
@@ -1638,7 +1929,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="D118" t="n">
         <v>340</v>
@@ -1651,7 +1942,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="D119" t="n">
         <v>1310</v>
@@ -1664,6 +1955,9 @@
         </is>
       </c>
       <c r="B120" t="n">
+        <v>4090</v>
+      </c>
+      <c r="D120" t="n">
         <v>3990</v>
       </c>
     </row>
@@ -1674,7 +1968,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="D121" t="n">
         <v>1370</v>
@@ -1687,6 +1981,9 @@
         </is>
       </c>
       <c r="B122" t="n">
+        <v>5150</v>
+      </c>
+      <c r="D122" t="n">
         <v>5180</v>
       </c>
     </row>
@@ -1697,6 +1994,9 @@
         </is>
       </c>
       <c r="B123" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D123" t="n">
         <v>6230</v>
       </c>
     </row>
@@ -1707,6 +2007,9 @@
         </is>
       </c>
       <c r="B124" t="n">
+        <v>3400</v>
+      </c>
+      <c r="D124" t="n">
         <v>3490</v>
       </c>
     </row>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>47310</v>
+        <v>44910</v>
       </c>
       <c r="D17" t="n">
         <v>47280</v>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>77310</v>
+        <v>71310</v>
       </c>
       <c r="D26" t="n">
         <v>77280</v>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,10 +459,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4090</v>
+        <v>2350</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>4120</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +477,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1300</v>
+        <v>950</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>1320</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5">
@@ -498,10 +508,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2700</v>
+        <v>1850</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>2720</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +692,15 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5500</v>
+        <v>3850</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>5590</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="21">
@@ -690,10 +710,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5500</v>
+        <v>3850</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>5590</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="22">
@@ -1243,7 +1268,15 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2700</v>
+        <v>2250</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2250</v>
       </c>
     </row>
     <row r="65">
@@ -1279,10 +1312,15 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2700</v>
+        <v>1850</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="D67" t="n">
-        <v>2720</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="68">
@@ -1367,10 +1405,15 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>940</v>
+        <v>450</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="D74" t="n">
-        <v>900</v>
+        <v>450</v>
       </c>
     </row>
     <row r="75">
@@ -1426,10 +1469,15 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2700</v>
+        <v>1850</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
       <c r="D79" t="n">
-        <v>2720</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="80">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>доля</t>
+          <t>прибыль</t>
         </is>
       </c>
     </row>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,10 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>670</v>
-      </c>
-      <c r="D2" t="n">
-        <v>620</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3">
@@ -466,9 +463,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2350</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -484,9 +478,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>950</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -495,10 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71310</v>
-      </c>
-      <c r="D5" t="n">
-        <v>70800</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="6">
@@ -515,9 +503,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1850</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -526,10 +511,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>940</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -539,10 +521,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6550</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6640</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="9">
@@ -552,10 +531,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>670</v>
-      </c>
-      <c r="D9" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10">
@@ -565,10 +541,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3050</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2890</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="11">
@@ -578,10 +551,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>670</v>
-      </c>
-      <c r="D11" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +561,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>940</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13">
@@ -604,10 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1780</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14">
@@ -617,10 +581,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1390</v>
+        <v>950</v>
       </c>
     </row>
     <row r="15">
@@ -630,10 +591,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8300</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8390</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="16">
@@ -643,7 +601,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6900</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="17">
@@ -653,10 +611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44910</v>
-      </c>
-      <c r="D17" t="n">
-        <v>47280</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="18">
@@ -666,10 +621,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2350</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2440</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="19">
@@ -681,9 +633,6 @@
       <c r="B19" t="n">
         <v>2700</v>
       </c>
-      <c r="D19" t="n">
-        <v>2720</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -699,9 +648,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>3850</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -717,9 +663,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>3850</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -728,10 +671,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9000</v>
-      </c>
-      <c r="D22" t="n">
-        <v>9020</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="23">
@@ -741,10 +681,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2020</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="24">
@@ -754,10 +691,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2720</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="25">
@@ -767,10 +701,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>41310</v>
-      </c>
-      <c r="D25" t="n">
-        <v>41280</v>
+        <v>36500</v>
       </c>
     </row>
     <row r="26">
@@ -780,10 +711,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>71310</v>
-      </c>
-      <c r="D26" t="n">
-        <v>77280</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="27">
@@ -793,10 +721,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>670</v>
-      </c>
-      <c r="D27" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28">
@@ -806,10 +731,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4450</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4240</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="29">
@@ -819,10 +741,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2720</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="30">
@@ -832,10 +751,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1390</v>
+        <v>950</v>
       </c>
     </row>
     <row r="31">
@@ -845,10 +761,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2020</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="32">
@@ -858,10 +771,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>940</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
     </row>
     <row r="33">
@@ -871,10 +781,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D33" t="n">
-        <v>6220</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="34">
@@ -884,10 +791,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D34" t="n">
-        <v>6290</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="35">
@@ -897,10 +801,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>940</v>
-      </c>
-      <c r="D35" t="n">
-        <v>870</v>
+        <v>950</v>
       </c>
     </row>
     <row r="36">
@@ -910,10 +811,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1320</v>
+        <v>950</v>
       </c>
     </row>
     <row r="37">
@@ -923,10 +821,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3050</v>
-      </c>
-      <c r="D37" t="n">
-        <v>3140</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="38">
@@ -936,10 +831,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>47310</v>
-      </c>
-      <c r="D38" t="n">
-        <v>47090</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="39">
@@ -949,10 +841,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3050</v>
-      </c>
-      <c r="D39" t="n">
-        <v>3140</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="40">
@@ -962,10 +851,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>670</v>
-      </c>
-      <c r="D40" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41">
@@ -975,10 +861,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>940</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
     </row>
     <row r="42">
@@ -988,10 +871,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>940</v>
-      </c>
-      <c r="D42" t="n">
-        <v>870</v>
+        <v>950</v>
       </c>
     </row>
     <row r="43">
@@ -1001,10 +881,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D43" t="n">
-        <v>6220</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="44">
@@ -1014,10 +891,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2530</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="45">
@@ -1027,7 +901,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="46">
@@ -1037,10 +911,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2020</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="47">
@@ -1050,7 +921,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="48">
@@ -1060,10 +931,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1720</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="49">
@@ -1073,10 +941,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2000</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="50">
@@ -1086,10 +951,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8300</v>
-      </c>
-      <c r="D50" t="n">
-        <v>8390</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="51">
@@ -1099,10 +961,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>670</v>
-      </c>
-      <c r="D51" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
     </row>
     <row r="52">
@@ -1112,10 +971,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11800</v>
-      </c>
-      <c r="D52" t="n">
-        <v>11820</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="53">
@@ -1125,10 +981,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>670</v>
-      </c>
-      <c r="D53" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54">
@@ -1138,10 +991,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1130</v>
+        <v>950</v>
       </c>
     </row>
     <row r="55">
@@ -1151,10 +1001,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>940</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
     </row>
     <row r="56">
@@ -1164,10 +1011,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>670</v>
-      </c>
-      <c r="D56" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57">
@@ -1177,10 +1021,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1130</v>
+        <v>950</v>
       </c>
     </row>
     <row r="58">
@@ -1190,10 +1031,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>940</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
     </row>
     <row r="59">
@@ -1203,10 +1041,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>35310</v>
-      </c>
-      <c r="D59" t="n">
-        <v>35340</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="60">
@@ -1216,10 +1051,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>35310</v>
-      </c>
-      <c r="D60" t="n">
-        <v>35340</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="61">
@@ -1229,10 +1061,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>35310</v>
-      </c>
-      <c r="D61" t="n">
-        <v>35340</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="62">
@@ -1242,10 +1071,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>670</v>
-      </c>
-      <c r="D62" t="n">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row r="63">
@@ -1255,10 +1081,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13900</v>
-      </c>
-      <c r="D63" t="n">
-        <v>13860</v>
+        <v>10850</v>
       </c>
     </row>
     <row r="64">
@@ -1275,9 +1098,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>2250</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1286,10 +1106,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>670</v>
-      </c>
-      <c r="D65" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
     </row>
     <row r="66">
@@ -1299,10 +1116,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D66" t="n">
-        <v>6220</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="67">
@@ -1319,9 +1133,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>1850</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1330,10 +1141,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D68" t="n">
-        <v>3320</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="69">
@@ -1343,10 +1151,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D69" t="n">
-        <v>4680</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="70">
@@ -1356,10 +1161,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1660</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="71">
@@ -1369,7 +1171,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -1379,10 +1181,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>670</v>
-      </c>
-      <c r="D72" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73">
@@ -1392,10 +1191,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>670</v>
-      </c>
-      <c r="D73" t="n">
-        <v>690</v>
+        <v>950</v>
       </c>
     </row>
     <row r="74">
@@ -1412,9 +1208,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>450</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1423,7 +1216,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1650</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="76">
@@ -1433,10 +1226,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D76" t="n">
-        <v>6220</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="77">
@@ -1446,10 +1236,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>9000</v>
-      </c>
-      <c r="D77" t="n">
-        <v>9090</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="78">
@@ -1459,7 +1246,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
     </row>
     <row r="79">
@@ -1476,9 +1263,6 @@
           <t>да</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>1850</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1487,10 +1271,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1370</v>
+        <v>950</v>
       </c>
     </row>
     <row r="81">
@@ -1502,9 +1283,6 @@
       <c r="B81" t="n">
         <v>670</v>
       </c>
-      <c r="D81" t="n">
-        <v>690</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1513,10 +1291,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D82" t="n">
-        <v>2020</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="83">
@@ -1526,10 +1301,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>670</v>
-      </c>
-      <c r="D83" t="n">
-        <v>340</v>
+        <v>450</v>
       </c>
     </row>
     <row r="84">
@@ -1541,9 +1313,6 @@
       <c r="B84" t="n">
         <v>940</v>
       </c>
-      <c r="D84" t="n">
-        <v>690</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1552,10 +1321,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D85" t="n">
-        <v>690</v>
+        <v>950</v>
       </c>
     </row>
     <row r="86">
@@ -1565,10 +1331,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D86" t="n">
-        <v>5250</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="87">
@@ -1578,10 +1341,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D87" t="n">
-        <v>5250</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="88">
@@ -1591,10 +1351,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D88" t="n">
-        <v>5950</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="89">
@@ -1604,10 +1361,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D89" t="n">
-        <v>5950</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="90">
@@ -1617,10 +1371,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6900</v>
-      </c>
-      <c r="D90" t="n">
-        <v>6650</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="91">
@@ -1632,9 +1383,6 @@
       <c r="B91" t="n">
         <v>6900</v>
       </c>
-      <c r="D91" t="n">
-        <v>6650</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1643,10 +1391,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D92" t="n">
-        <v>5950</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="93">
@@ -1671,10 +1416,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D94" t="n">
-        <v>5950</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="95">
@@ -1684,10 +1426,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>6900</v>
-      </c>
-      <c r="D95" t="n">
-        <v>6650</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="96">
@@ -1697,10 +1436,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>6900</v>
-      </c>
-      <c r="D96" t="n">
-        <v>6650</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="97">
@@ -1710,10 +1446,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D97" t="n">
-        <v>870</v>
+        <v>950</v>
       </c>
     </row>
     <row r="98">
@@ -1723,10 +1456,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D98" t="n">
-        <v>2790</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="99">
@@ -1736,10 +1466,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D99" t="n">
-        <v>2790</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="100">
@@ -1749,10 +1476,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>940</v>
-      </c>
-      <c r="D100" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
     </row>
     <row r="101">
@@ -1762,10 +1486,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>670</v>
-      </c>
-      <c r="D101" t="n">
-        <v>590</v>
+        <v>450</v>
       </c>
     </row>
     <row r="102">
@@ -1777,9 +1498,6 @@
       <c r="B102" t="n">
         <v>320</v>
       </c>
-      <c r="D102" t="n">
-        <v>410</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1790,9 +1508,6 @@
       <c r="B103" t="n">
         <v>320</v>
       </c>
-      <c r="D103" t="n">
-        <v>410</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1801,10 +1516,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D104" t="n">
-        <v>2090</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="105">
@@ -1814,10 +1526,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D105" t="n">
-        <v>2090</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="106">
@@ -1847,10 +1556,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>940</v>
-      </c>
-      <c r="D108" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
     </row>
     <row r="109">
@@ -1860,10 +1566,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>940</v>
-      </c>
-      <c r="D109" t="n">
-        <v>1040</v>
+        <v>950</v>
       </c>
     </row>
     <row r="110">
@@ -1873,10 +1576,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D110" t="n">
-        <v>1740</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="111">
@@ -1886,10 +1586,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D111" t="n">
-        <v>1180</v>
+        <v>950</v>
       </c>
     </row>
     <row r="112">
@@ -1899,10 +1596,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D112" t="n">
-        <v>1320</v>
+        <v>950</v>
       </c>
     </row>
     <row r="113">
@@ -1912,10 +1606,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D113" t="n">
-        <v>1370</v>
+        <v>950</v>
       </c>
     </row>
     <row r="114">
@@ -1925,10 +1616,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>940</v>
-      </c>
-      <c r="D114" t="n">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row r="115">
@@ -1938,10 +1626,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>940</v>
-      </c>
-      <c r="D115" t="n">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row r="116">
@@ -1951,10 +1636,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>940</v>
-      </c>
-      <c r="D116" t="n">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row r="117">
@@ -1964,10 +1646,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>940</v>
-      </c>
-      <c r="D117" t="n">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row r="118">
@@ -1977,10 +1656,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>670</v>
-      </c>
-      <c r="D118" t="n">
-        <v>340</v>
+        <v>450</v>
       </c>
     </row>
     <row r="119">
@@ -1992,9 +1668,6 @@
       <c r="B119" t="n">
         <v>1650</v>
       </c>
-      <c r="D119" t="n">
-        <v>1310</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2005,9 +1678,6 @@
       <c r="B120" t="n">
         <v>4090</v>
       </c>
-      <c r="D120" t="n">
-        <v>3990</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2016,10 +1686,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D121" t="n">
-        <v>1370</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="122">
@@ -2029,10 +1696,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5150</v>
-      </c>
-      <c r="D122" t="n">
-        <v>5180</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="123">
@@ -2042,10 +1706,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D123" t="n">
-        <v>6230</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="124">
@@ -2055,10 +1716,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D124" t="n">
-        <v>3490</v>
+        <v>2350</v>
       </c>
     </row>
   </sheetData>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3350</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="29">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="24">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="47">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1730,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,6 +1815,16 @@
         <v>0.03</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Мин. чистая прибыль Авито/сайта, доля от закупки (1 = 100%)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1730,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1825,6 +1825,16 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Дорогие позиции (цена Ozon от, ₽): цену Авито/сайта не пересчитывать</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5850</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="16">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3350</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="44">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3850</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="88">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="10">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="12">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="28">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="41">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="54">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="57">
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="66">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="73">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="79">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="81">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="84">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="102">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
     </row>
     <row r="119">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1730,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,6 +1815,26 @@
         <v>0.03</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Мин. чистая прибыль Авито/сайта, доля от закупки (1 = 100%)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Дорогие позиции (цена Ozon от, ₽): цену Авито/сайта не пересчитывать</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -953,6 +953,11 @@
       <c r="B50" t="n">
         <v>5850</v>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="9">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6350</v>
+        <v>7850</v>
       </c>
     </row>
     <row r="16">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4850</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="17">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6350</v>
+        <v>7850</v>
       </c>
     </row>
     <row r="23">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="25">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="29">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="30">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="34">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="35">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3850</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="44">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="45">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="46">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="48">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8850</v>
+        <v>9850</v>
       </c>
     </row>
     <row r="53">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10850</v>
+        <v>11850</v>
       </c>
     </row>
     <row r="64">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="67">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="69">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3350</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="70">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="77">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6350</v>
+        <v>7350</v>
       </c>
     </row>
     <row r="78">
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
     </row>
     <row r="85">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5150</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="87">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="88">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="89">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="90">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="91">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="93">
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="95">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="96">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="97">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="99">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="100">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>320</v>
+        <v>450</v>
       </c>
     </row>
     <row r="103">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>320</v>
+        <v>450</v>
       </c>
     </row>
     <row r="104">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="122">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3850</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="123">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="124">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
     </row>
   </sheetData>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1501,7 +1501,12 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>450</v>
+        <v>650</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -1511,7 +1516,12 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>450</v>
+        <v>650</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="104">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2700</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="20">
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>670</v>
+        <v>950</v>
       </c>
     </row>
     <row r="82">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6900</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="92">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1990</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="107">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1990</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="108">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1650</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="120">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4090</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="121">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="120">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1732,6 +1732,26 @@
       </c>
       <c r="B124" t="n">
         <v>2850</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>0AM927769F</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>0am325025HXF</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>68500</v>
       </c>
     </row>
   </sheetData>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,42 +617,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0AM927769F</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1850</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2850</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3850</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>2850</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -667,107 +662,112 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7850</v>
+        <v>3850</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1850</v>
+        <v>7850</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2350</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>36500</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>68500</v>
+        <v>36500</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>950</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025HXF</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2850</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>950</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1350</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -777,97 +777,97 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4850</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4850</v>
+        <v>950</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>950</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>950</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2850</v>
+        <v>950</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>42500</v>
+        <v>950</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>950</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>950</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -877,47 +877,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4850</v>
+        <v>950</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -927,62 +927,62 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1350</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5850</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>1350</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9850</v>
+        <v>5850</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -992,17 +992,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>950</v>
+        <v>10850</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1012,7 +1012,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1022,7 +1022,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1032,7 +1032,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1042,27 +1042,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32500</v>
+        <v>950</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32500</v>
+        <v>950</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1072,227 +1072,227 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>950</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>11850</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2250</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>950</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>950</v>
+        <v>11850</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4850</v>
+        <v>2250</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>950</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2850</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3850</v>
+        <v>1850</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1350</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>100</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>450</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>950</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4850</v>
+        <v>450</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>7350</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>950</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>7350</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>950</v>
+        <v>1850</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1302,7 +1302,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1312,17 +1312,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1332,272 +1332,272 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>5350</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>5350</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5350</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6850</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5350</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>5850</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>8350</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4850</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5350</v>
+        <v>5850</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5350</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>950</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2350</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>950</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>950</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>650</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>950</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>650</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+        <v>950</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1350</v>
+        <v>650</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1350</v>
+        <v>650</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>950</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>950</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -1607,17 +1607,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -1627,7 +1627,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -1637,7 +1637,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -1647,7 +1647,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -1657,7 +1657,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1667,7 +1667,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1677,37 +1677,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4350</v>
+        <v>950</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -1717,41 +1717,41 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4850</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2850</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0AM927769F</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>42500</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0am325025HXF</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>68500</v>
+        <v>2850</v>
       </c>
     </row>
   </sheetData>

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>950</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="33">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены Avito и сайт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,7 +611,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42500</v>
+        <v>39500</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -621,7 +626,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42500</v>
+        <v>39500</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -711,7 +721,12 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>36500</v>
+        <v>33500</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -851,7 +866,12 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>42500</v>
+        <v>38500</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="41">

--- a/data/avito_site_price_overrides.xlsx
+++ b/data/avito_site_price_overrides.xlsx
@@ -736,7 +736,12 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>68500</v>
+        <v>64500</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -746,7 +751,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>68500</v>
+        <v>64500</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="29">
